--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -136,7 +136,7 @@
     <t>jpa_version</t>
   </si>
   <si>
-    <t>///@javaVersion</t>
+    <t>///@optimisticlock</t>
   </si>
   <si>
     <t>create_time</t>
@@ -617,7 +617,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,13 +637,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1108,148 +1101,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="2" r:id="rId1"/>
     <sheet name="tm_teacher@" sheetId="3" r:id="rId2"/>
     <sheet name="tbl_3ds_request" sheetId="4" r:id="rId3"/>
     <sheet name="tbl_3ds_request@" sheetId="5" r:id="rId4"/>
+    <sheet name="tm_student" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="196">
   <si>
     <t>表名</t>
   </si>
@@ -605,6 +606,24 @@
   </si>
   <si>
     <t>RETRIEVAL_REFERENCE_NUMBER = @RRN</t>
+  </si>
+  <si>
+    <t>tm_student</t>
+  </si>
+  <si>
+    <t>tenant_id</t>
+  </si>
+  <si>
+    <t>student_no</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>enroll_date</t>
+  </si>
+  <si>
+    <t>is_graduate</t>
   </si>
 </sst>
 </file>
@@ -617,7 +636,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,13 +656,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1108,28 +1120,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1138,118 +1153,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4494,4 +4506,745 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="2" r:id="rId1"/>
@@ -17,6 +17,9 @@
     <sheet name="tbl_3ds_request" sheetId="4" r:id="rId3"/>
     <sheet name="tbl_3ds_request@" sheetId="5" r:id="rId4"/>
     <sheet name="tm_student" sheetId="6" r:id="rId5"/>
+    <sheet name="tm_no_primary" sheetId="7" r:id="rId6"/>
+    <sheet name="tm_no_index" sheetId="8" r:id="rId7"/>
+    <sheet name="tm_no" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="199">
   <si>
     <t>表名</t>
   </si>
@@ -624,6 +627,15 @@
   </si>
   <si>
     <t>is_graduate</t>
+  </si>
+  <si>
+    <t>tm_no_primary</t>
+  </si>
+  <si>
+    <t>tm_no_index</t>
+  </si>
+  <si>
+    <t>tm_no</t>
   </si>
 </sst>
 </file>
@@ -5247,4 +5259,1937 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -9,13 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="2" r:id="rId1"/>
     <sheet name="tm_teacher@" sheetId="3" r:id="rId2"/>
     <sheet name="tbl_3ds_request" sheetId="4" r:id="rId3"/>
     <sheet name="tbl_3ds_request@" sheetId="5" r:id="rId4"/>
+    <sheet name="tm_student" sheetId="6" r:id="rId5"/>
+    <sheet name="tm_no_primary" sheetId="7" r:id="rId6"/>
+    <sheet name="tm_no_index" sheetId="8" r:id="rId7"/>
+    <sheet name="tm_no" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="199">
   <si>
     <t>表名</t>
   </si>
@@ -605,6 +609,33 @@
   </si>
   <si>
     <t>RETRIEVAL_REFERENCE_NUMBER = @RRN</t>
+  </si>
+  <si>
+    <t>tm_student</t>
+  </si>
+  <si>
+    <t>tenant_id</t>
+  </si>
+  <si>
+    <t>student_no</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>enroll_date</t>
+  </si>
+  <si>
+    <t>is_graduate</t>
+  </si>
+  <si>
+    <t>tm_no_primary</t>
+  </si>
+  <si>
+    <t>tm_no_index</t>
+  </si>
+  <si>
+    <t>tm_no</t>
   </si>
 </sst>
 </file>
@@ -617,7 +648,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,13 +668,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1108,28 +1132,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1138,118 +1165,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4494,4 +4518,2678 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>